--- a/templates/Grafik-dane-2026-08-przyklad.xlsx
+++ b/templates/Grafik-dane-2026-08-przyklad.xlsx
@@ -18,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="12">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0 &quot;h&quot;"/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,25 +31,59 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F2430"/>
+      <color rgb="0010281E"/>
       <sz val="20"/>
     </font>
     <font>
-      <color rgb="006B7280"/>
+      <color rgb="006B7A72"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="004F46E5"/>
+      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
-      <color rgb="001F2430"/>
+      <b val="1"/>
+      <color rgb="0010281E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="0010281E"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Menlo"/>
-      <color rgb="001F2430"/>
+      <b val="1"/>
+      <color rgb="001D7645"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008C2F2F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008A5A12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="003A3E8F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7A72"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0010281E"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <color rgb="006B7A72"/>
       <sz val="11"/>
     </font>
     <font>
@@ -57,29 +93,49 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F2430"/>
+      <color rgb="006B7A72"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="004F46E5"/>
+      <color rgb="008C2F2F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="006B7A72"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008A5A12"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="003A3E8F"/>
       <sz val="11"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="006B7A72"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="006B7280"/>
+      <b val="1"/>
+      <color rgb="006B7A72"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="006B7A72"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B7A72"/>
       <sz val="10"/>
     </font>
-    <font>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -88,16 +144,51 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F2430"/>
+        <fgColor rgb="001D7645"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF0F5"/>
+        <fgColor rgb="00FCE3E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEFD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E4FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010281E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FBF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF3F1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -106,58 +197,123 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00DCE6E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DCE6E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCE6E1"/>
+      </top>
       <bottom style="thin">
-        <color rgb="001F2430"/>
+        <color rgb="00DCE6E1"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="001D7645"/>
       </bottom>
     </border>
     <border>
       <right style="thin">
-        <color rgb="00D8DCE6"/>
+        <color rgb="00DCE6E1"/>
       </right>
       <bottom style="thin">
-        <color rgb="00D8DCE6"/>
+        <color rgb="00DCE6E1"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -165,23 +321,35 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="008C2F2F"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FBD5D5"/>
+          <fgColor rgb="00FCE3E3"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="008A5A12"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FDE7C3"/>
+          <fgColor rgb="00FDEFD5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="003A3E8F"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00D9DBF7"/>
+          <fgColor rgb="00E2E4FA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -264,42 +432,42 @@
     <author>Grafik</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A3" authorId="0" shapeId="0">
       <text>
-        <t>Dokładnie tak samo jak w zakładce Dostępność.</t>
+        <t>Tak samo jak w zakładce Dostępność — najlepiej wybierz siebie z listy.</t>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B3" authorId="0" shapeId="0">
       <text>
-        <t>Ile godzin chcesz przepracować w tym miesiącu.</t>
+        <t>Ile godzin chcesz przepracować w tym miesiącu. Liczba, np. 160.</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Dzień, Noc albo Bez preferencji.</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D3" authorId="0" shapeId="0">
       <text>
-        <t>Czy chcesz dyżury 24-godzinne i w jakim układzie.</t>
+        <t>Czy bierzesz dyżury 24-godzinne i w jakim układzie.</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E3" authorId="0" shapeId="0">
       <text>
-        <t>Kwalifikacje, po przecinku. Domyślnie: General.</t>
+        <t>Twoje kwalifikacje, po przecinku. Domyślnie: General.</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Tak, jeśli możesz pełnić zmianę kierownika.</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Tak tylko dla jednej osoby w zespole.</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Pole dowolne — program je pomija.</t>
       </text>
@@ -594,153 +762,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001D7645"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="108" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Grafik — dane od pracowników</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Wypełnij swój wiersz w obu zakładkach. Zajmuje to około dwóch minut.</t>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>sierpień 2026 · wypełnij swój wiersz w obu zakładkach, zajmuje to około dwóch minut</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1">
       <c r="A3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
+      <c r="B3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Krok 1 — zakładka „Pracownicy”</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Znajdź swoje imię i nazwisko (albo dopisz je w pierwszym wolnym wierszu) i uzupełnij: ile godzin chcesz przepracować w tym miesiącu, jaką porę dnia wolisz i czy bierzesz dyżury 24h. Kolumny z listą rozwijaną wypełnij wyłącznie wartościami z listy.</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Zakładka „Pracownicy”</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Znajdź swoje imię i nazwisko albo dopisz je w pierwszym wolnym wierszu. Uzupełnij, ile godzin chcesz przepracować, jaką porę dnia wolisz i czy bierzesz dyżury 24h. Komórki z listą rozwijaną wypełnij wyłącznie wartościami z listy.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="8" customHeight="1">
       <c r="A6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Krok 2 — zakładka „Dostępność”</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>W swoim wierszu zaznacz dni, w których NIE możesz pracować. Puste pole oznacza, że jesteś dostępny — nie musisz nic wpisywać przy dniach, w które możesz pracować.</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Zakładka „Dostępność”</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>W swoim wierszu zaznacz tylko te dni, w których NIE możesz pracować. Puste pole znaczy, że jesteś dostępny — przy dniach, w które możesz pracować, nie wpisuj niczego.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="8" customHeight="1">
       <c r="A9" t="inlineStr"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Legenda kodów dostępności</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>X    niedostępny przez cały dzień (np. urlop, L4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>D    niedostępny rano i w dzień — zmiany nocne są w porządku</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>N    niedostępny w nocy — zmiany dzienne są w porządku</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     puste pole — jestem dostępny</t>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Kody dostępności</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>niedostępny przez cały dzień (urlop, L4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>niedostępny rano i w dzień — noce są w porządku</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>niedostępny w nocy — dni są w porządku</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>puste pole — jestem dostępny</t>
         </is>
       </c>
     </row>
     <row r="15" ht="8" customHeight="1">
       <c r="A15" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>O czym pamiętać</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>• Imię i nazwisko musi brzmieć tak samo w obu zakładkach — w zakładce „Dostępność” wybierz je z listy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>• Nie zmieniaj nazw zakładek ani nagłówków kolumn — po nich program rozpoznaje dane.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>• Możesz dopisywać wiersze na dole i dodawać własne kolumny; program pomija to, czego nie zna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>• Miesiąc, którego dotyczy arkusz, jest wpisany w komórce B1 zakładki „Dostępność”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="8" customHeight="1">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Imię i nazwisko musi brzmieć tak samo w obu zakładkach — w „Dostępności” wybierz je z listy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Nie zmieniaj nazw zakładek ani nagłówków kolumn — po nich program rozpoznaje dane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Możesz dopisywać wiersze na dole i dodawać własne kolumny; program pomija to, czego nie zna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
       <c r="A21" t="inlineStr"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Dla osoby układającej grafik</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Gdy zespół skończy wypełniać: Plik → Pobierz → Microsoft Excel (.xlsx). Następnie w programie Shiftwise: zakładka Workers → Import from sheet → wskaż pobrany plik. Przed zapisem zobaczysz podgląd tego, co zostanie zmienione.</t>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Gdy zespół skończy: Plik → Pobierz → Microsoft Excel (.xlsx), a następnie w programie Shiftwise zakładka Workers → Import from sheet. Przed zapisem zobaczysz podgląd wszystkich zmian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Miesiąc, którego dotyczy arkusz, jest w komórce B1 zakładki „Dostępność”. Aby użyć tego samego arkusza w kolejnym miesiącu, zmień tę komórkę i wyczyść siatkę.</t>
         </is>
       </c>
     </row>
@@ -752,343 +965,326 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0010281E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Pracownicy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Jeden wiersz na osobę · sierpień 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Imię i nazwisko</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Godziny docelowe</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Preferowana pora</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Dyżur 24h</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Kategorie</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>Uprawnienia kierownika</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Kierownik domyślny</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>Uwagi</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Łukasz Zieliński</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B4" s="16" t="n">
         <v>160</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Dzień</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Nie</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
       </c>
-      <c r="H2" s="7" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="H4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Agnieszka Wójcik</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B5" s="19" t="n">
         <v>152</v>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Noc</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Dowolny</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>Nie</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>Nie</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>Wolę bloki nocne.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Paweł Nowak</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B6" s="16" t="n">
         <v>168</v>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Bez preferencji</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>08:00 → 08:00</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Nie</t>
         </is>
       </c>
-      <c r="H4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="H6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Maja Dąbrowska</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B7" s="19" t="n">
         <v>144</v>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Dzień</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Nie</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>Nie</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>Nie</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>Urlop w drugim tygodniu.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="18" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="18" t="n"/>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="18" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="C2:C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Preferowana pora" error="Wybierz: Dzień, Noc albo Bez preferencji." promptTitle="Preferowana pora" prompt="Wybierz: Dzień, Noc albo Bez preferencji." type="list">
+    <dataValidation sqref="C4:C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Preferowana pora" error="Wybierz: Dzień, Noc albo Bez preferencji." promptTitle="Preferowana pora" prompt="Wybierz: Dzień, Noc albo Bez preferencji." type="list">
       <formula1>"Dzień,Noc,Bez preferencji"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Dyżur 24h" error="Nie, Dowolny albo konkretny układ 24-godzinny." promptTitle="Dyżur 24h" prompt="Nie, Dowolny albo konkretny układ 24-godzinny." type="list">
+    <dataValidation sqref="D4:D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Dyżur 24h" error="Nie, Dowolny albo konkretny układ 24-godzinny." promptTitle="Dyżur 24h" prompt="Nie, Dowolny albo konkretny układ 24-godzinny." type="list">
       <formula1>"Nie,Dowolny,08:00 → 08:00,20:00 → 20:00"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Uprawnienia kierownika" error="Tak albo Nie." promptTitle="Uprawnienia kierownika" prompt="Tak albo Nie." type="list">
+    <dataValidation sqref="F4:F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Uprawnienia kierownika" error="Tak albo Nie." promptTitle="Uprawnienia kierownika" prompt="Tak albo Nie." type="list">
       <formula1>"Tak,Nie"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Kierownik domyślny" error="Tak tylko dla jednej osoby w zespole." promptTitle="Kierownik domyślny" prompt="Tak tylko dla jednej osoby w zespole." type="list">
+    <dataValidation sqref="G4:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Kierownik domyślny" error="Tak tylko dla jednej osoby w zespole." promptTitle="Kierownik domyślny" prompt="Tak tylko dla jednej osoby w zespole." type="list">
       <formula1>"Tak,Nie"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Godziny docelowe" error="Podaj liczbę godzin z zakresu 0–400." type="whole" operator="between">
+    <dataValidation sqref="B4:B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Godziny docelowe" error="Podaj liczbę godzin z zakresu 0–400." promptTitle="Godziny docelowe" prompt="Ile godzin chcesz przepracować w tym miesiącu." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>400</formula2>
     </dataValidation>
@@ -1101,340 +1297,377 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001D7645"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF16"/>
+  <dimension ref="A1:AG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="4.4" customWidth="1" min="2" max="2"/>
-    <col width="4.4" customWidth="1" min="3" max="3"/>
-    <col width="4.4" customWidth="1" min="4" max="4"/>
-    <col width="4.4" customWidth="1" min="5" max="5"/>
-    <col width="4.4" customWidth="1" min="6" max="6"/>
-    <col width="4.4" customWidth="1" min="7" max="7"/>
-    <col width="4.4" customWidth="1" min="8" max="8"/>
-    <col width="4.4" customWidth="1" min="9" max="9"/>
-    <col width="4.4" customWidth="1" min="10" max="10"/>
-    <col width="4.4" customWidth="1" min="11" max="11"/>
-    <col width="4.4" customWidth="1" min="12" max="12"/>
-    <col width="4.4" customWidth="1" min="13" max="13"/>
-    <col width="4.4" customWidth="1" min="14" max="14"/>
-    <col width="4.4" customWidth="1" min="15" max="15"/>
-    <col width="4.4" customWidth="1" min="16" max="16"/>
-    <col width="4.4" customWidth="1" min="17" max="17"/>
-    <col width="4.4" customWidth="1" min="18" max="18"/>
-    <col width="4.4" customWidth="1" min="19" max="19"/>
-    <col width="4.4" customWidth="1" min="20" max="20"/>
-    <col width="4.4" customWidth="1" min="21" max="21"/>
-    <col width="4.4" customWidth="1" min="22" max="22"/>
-    <col width="4.4" customWidth="1" min="23" max="23"/>
-    <col width="4.4" customWidth="1" min="24" max="24"/>
-    <col width="4.4" customWidth="1" min="25" max="25"/>
-    <col width="4.4" customWidth="1" min="26" max="26"/>
-    <col width="4.4" customWidth="1" min="27" max="27"/>
-    <col width="4.4" customWidth="1" min="28" max="28"/>
-    <col width="4.4" customWidth="1" min="29" max="29"/>
-    <col width="4.4" customWidth="1" min="30" max="30"/>
-    <col width="4.4" customWidth="1" min="31" max="31"/>
-    <col width="4.4" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="4.2" customWidth="1" min="2" max="2"/>
+    <col width="4.2" customWidth="1" min="3" max="3"/>
+    <col width="4.2" customWidth="1" min="4" max="4"/>
+    <col width="4.2" customWidth="1" min="5" max="5"/>
+    <col width="4.2" customWidth="1" min="6" max="6"/>
+    <col width="4.2" customWidth="1" min="7" max="7"/>
+    <col width="4.2" customWidth="1" min="8" max="8"/>
+    <col width="4.2" customWidth="1" min="9" max="9"/>
+    <col width="4.2" customWidth="1" min="10" max="10"/>
+    <col width="4.2" customWidth="1" min="11" max="11"/>
+    <col width="4.2" customWidth="1" min="12" max="12"/>
+    <col width="4.2" customWidth="1" min="13" max="13"/>
+    <col width="4.2" customWidth="1" min="14" max="14"/>
+    <col width="4.2" customWidth="1" min="15" max="15"/>
+    <col width="4.2" customWidth="1" min="16" max="16"/>
+    <col width="4.2" customWidth="1" min="17" max="17"/>
+    <col width="4.2" customWidth="1" min="18" max="18"/>
+    <col width="4.2" customWidth="1" min="19" max="19"/>
+    <col width="4.2" customWidth="1" min="20" max="20"/>
+    <col width="4.2" customWidth="1" min="21" max="21"/>
+    <col width="4.2" customWidth="1" min="22" max="22"/>
+    <col width="4.2" customWidth="1" min="23" max="23"/>
+    <col width="4.2" customWidth="1" min="24" max="24"/>
+    <col width="4.2" customWidth="1" min="25" max="25"/>
+    <col width="4.2" customWidth="1" min="26" max="26"/>
+    <col width="4.2" customWidth="1" min="27" max="27"/>
+    <col width="4.2" customWidth="1" min="28" max="28"/>
+    <col width="4.2" customWidth="1" min="29" max="29"/>
+    <col width="4.2" customWidth="1" min="30" max="30"/>
+    <col width="4.2" customWidth="1" min="31" max="31"/>
+    <col width="4.2" customWidth="1" min="32" max="32"/>
+    <col width="8" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Miesiąc</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>Format RRRR-MM. Zmień, jeśli arkusz dotyczy innego miesiąca.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>X = cały dzień   ·   D = rano / dzień   ·   N = noc   ·   puste = dostępny</t>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Zaznacz tylko te dni, w których NIE możesz pracować — sierpień 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>cały dzień</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>rano / dzień</t>
+        </is>
+      </c>
+      <c r="P2" s="26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q2" s="24" t="inlineStr">
+        <is>
+          <t>noc</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>puste = dostępny</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Dzień tygodnia</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Nd</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>Pn</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>Wt</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>Śr</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t>Cz</t>
         </is>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="H3" s="29" t="inlineStr">
         <is>
           <t>Pt</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="28" t="inlineStr">
         <is>
           <t>Nd</t>
         </is>
       </c>
-      <c r="K3" s="14" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t>Pn</t>
         </is>
       </c>
-      <c r="L3" s="14" t="inlineStr">
+      <c r="L3" s="29" t="inlineStr">
         <is>
           <t>Wt</t>
         </is>
       </c>
-      <c r="M3" s="14" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t>Śr</t>
         </is>
       </c>
-      <c r="N3" s="14" t="inlineStr">
+      <c r="N3" s="29" t="inlineStr">
         <is>
           <t>Cz</t>
         </is>
       </c>
-      <c r="O3" s="14" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t>Pt</t>
         </is>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="P3" s="28" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="Q3" s="28" t="inlineStr">
         <is>
           <t>Nd</t>
         </is>
       </c>
-      <c r="R3" s="14" t="inlineStr">
+      <c r="R3" s="29" t="inlineStr">
         <is>
           <t>Pn</t>
         </is>
       </c>
-      <c r="S3" s="14" t="inlineStr">
+      <c r="S3" s="29" t="inlineStr">
         <is>
           <t>Wt</t>
         </is>
       </c>
-      <c r="T3" s="14" t="inlineStr">
+      <c r="T3" s="29" t="inlineStr">
         <is>
           <t>Śr</t>
         </is>
       </c>
-      <c r="U3" s="14" t="inlineStr">
+      <c r="U3" s="29" t="inlineStr">
         <is>
           <t>Cz</t>
         </is>
       </c>
-      <c r="V3" s="14" t="inlineStr">
+      <c r="V3" s="29" t="inlineStr">
         <is>
           <t>Pt</t>
         </is>
       </c>
-      <c r="W3" s="13" t="inlineStr">
+      <c r="W3" s="28" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="X3" s="13" t="inlineStr">
+      <c r="X3" s="28" t="inlineStr">
         <is>
           <t>Nd</t>
         </is>
       </c>
-      <c r="Y3" s="14" t="inlineStr">
+      <c r="Y3" s="29" t="inlineStr">
         <is>
           <t>Pn</t>
         </is>
       </c>
-      <c r="Z3" s="14" t="inlineStr">
+      <c r="Z3" s="29" t="inlineStr">
         <is>
           <t>Wt</t>
         </is>
       </c>
-      <c r="AA3" s="14" t="inlineStr">
+      <c r="AA3" s="29" t="inlineStr">
         <is>
           <t>Śr</t>
         </is>
       </c>
-      <c r="AB3" s="14" t="inlineStr">
+      <c r="AB3" s="29" t="inlineStr">
         <is>
           <t>Cz</t>
         </is>
       </c>
-      <c r="AC3" s="14" t="inlineStr">
+      <c r="AC3" s="29" t="inlineStr">
         <is>
           <t>Pt</t>
         </is>
       </c>
-      <c r="AD3" s="13" t="inlineStr">
+      <c r="AD3" s="28" t="inlineStr">
         <is>
           <t>So</t>
         </is>
       </c>
-      <c r="AE3" s="13" t="inlineStr">
+      <c r="AE3" s="28" t="inlineStr">
         <is>
           <t>Nd</t>
         </is>
       </c>
-      <c r="AF3" s="14" t="inlineStr">
+      <c r="AF3" s="29" t="inlineStr">
         <is>
           <t>Pn</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Imię i nazwisko</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="K4" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="O4" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="P4" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="Q4" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="R4" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="S4" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="T4" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="U4" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="V4" s="6" t="n">
+      <c r="V4" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="W4" s="6" t="n">
+      <c r="W4" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="X4" s="6" t="n">
+      <c r="X4" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="Y4" s="6" t="n">
+      <c r="Y4" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="Z4" s="6" t="n">
+      <c r="Z4" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="AA4" s="6" t="n">
+      <c r="AA4" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="AB4" s="6" t="n">
+      <c r="AB4" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="AC4" s="6" t="n">
+      <c r="AC4" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AD4" s="6" t="n">
+      <c r="AD4" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="AE4" s="6" t="n">
+      <c r="AE4" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="AF4" s="6" t="n">
+      <c r="AF4" s="14" t="n">
         <v>31</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="AG4" s="14" t="inlineStr">
+        <is>
+          <t>Razem</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Łukasz Zieliński</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
       <c r="D5" s="17" t="inlineStr">
         <is>
           <t>N</t>
@@ -1448,15 +1681,15 @@
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="17" t="n"/>
       <c r="H5" s="17" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="16" t="n"/>
+      <c r="I5" s="32" t="n"/>
+      <c r="J5" s="32" t="n"/>
       <c r="K5" s="17" t="n"/>
       <c r="L5" s="17" t="n"/>
       <c r="M5" s="17" t="n"/>
       <c r="N5" s="17" t="n"/>
       <c r="O5" s="17" t="n"/>
-      <c r="P5" s="16" t="n"/>
-      <c r="Q5" s="16" t="n"/>
+      <c r="P5" s="32" t="n"/>
+      <c r="Q5" s="32" t="n"/>
       <c r="R5" s="17" t="inlineStr">
         <is>
           <t>X</t>
@@ -1466,86 +1699,94 @@
       <c r="T5" s="17" t="n"/>
       <c r="U5" s="17" t="n"/>
       <c r="V5" s="17" t="n"/>
-      <c r="W5" s="16" t="n"/>
-      <c r="X5" s="16" t="n"/>
+      <c r="W5" s="32" t="n"/>
+      <c r="X5" s="32" t="n"/>
       <c r="Y5" s="17" t="n"/>
       <c r="Z5" s="17" t="n"/>
       <c r="AA5" s="17" t="n"/>
       <c r="AB5" s="17" t="n"/>
       <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="16" t="n"/>
-      <c r="AE5" s="16" t="n"/>
+      <c r="AD5" s="32" t="n"/>
+      <c r="AE5" s="32" t="n"/>
       <c r="AF5" s="17" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="AG5" s="33">
+        <f>COUNTA(B5:AF5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Agnieszka Wójcik</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="17" t="n"/>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="B6" s="32" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="32" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="32" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="K6" s="17" t="n"/>
-      <c r="L6" s="17" t="n"/>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="17" t="n"/>
-      <c r="O6" s="17" t="n"/>
-      <c r="P6" s="16" t="n"/>
-      <c r="Q6" s="16" t="n"/>
-      <c r="R6" s="17" t="n"/>
-      <c r="S6" s="17" t="n"/>
-      <c r="T6" s="17" t="n"/>
-      <c r="U6" s="17" t="n"/>
-      <c r="V6" s="17" t="n"/>
-      <c r="W6" s="16" t="inlineStr">
+      <c r="K6" s="20" t="n"/>
+      <c r="L6" s="20" t="n"/>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="n"/>
+      <c r="P6" s="32" t="n"/>
+      <c r="Q6" s="32" t="n"/>
+      <c r="R6" s="20" t="n"/>
+      <c r="S6" s="20" t="n"/>
+      <c r="T6" s="20" t="n"/>
+      <c r="U6" s="20" t="n"/>
+      <c r="V6" s="20" t="n"/>
+      <c r="W6" s="32" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="X6" s="16" t="inlineStr">
+      <c r="X6" s="32" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Y6" s="17" t="n"/>
-      <c r="Z6" s="17" t="n"/>
-      <c r="AA6" s="17" t="n"/>
-      <c r="AB6" s="17" t="n"/>
-      <c r="AC6" s="17" t="n"/>
-      <c r="AD6" s="16" t="n"/>
-      <c r="AE6" s="16" t="n"/>
-      <c r="AF6" s="17" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="Y6" s="20" t="n"/>
+      <c r="Z6" s="20" t="n"/>
+      <c r="AA6" s="20" t="n"/>
+      <c r="AB6" s="20" t="n"/>
+      <c r="AC6" s="20" t="n"/>
+      <c r="AD6" s="32" t="n"/>
+      <c r="AE6" s="32" t="n"/>
+      <c r="AF6" s="20" t="n"/>
+      <c r="AG6" s="33">
+        <f>COUNTA(B6:AF6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Paweł Nowak</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="32" t="n"/>
       <c r="D7" s="17" t="n"/>
       <c r="E7" s="17" t="n"/>
       <c r="F7" s="17" t="n"/>
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="17" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="n"/>
+      <c r="I7" s="32" t="n"/>
+      <c r="J7" s="32" t="n"/>
       <c r="K7" s="17" t="n"/>
       <c r="L7" s="17" t="n"/>
       <c r="M7" s="17" t="inlineStr">
@@ -1555,355 +1796,398 @@
       </c>
       <c r="N7" s="17" t="n"/>
       <c r="O7" s="17" t="n"/>
-      <c r="P7" s="16" t="n"/>
-      <c r="Q7" s="16" t="n"/>
+      <c r="P7" s="32" t="n"/>
+      <c r="Q7" s="32" t="n"/>
       <c r="R7" s="17" t="n"/>
       <c r="S7" s="17" t="n"/>
       <c r="T7" s="17" t="n"/>
       <c r="U7" s="17" t="n"/>
       <c r="V7" s="17" t="n"/>
-      <c r="W7" s="16" t="n"/>
-      <c r="X7" s="16" t="n"/>
+      <c r="W7" s="32" t="n"/>
+      <c r="X7" s="32" t="n"/>
       <c r="Y7" s="17" t="n"/>
       <c r="Z7" s="17" t="n"/>
       <c r="AA7" s="17" t="n"/>
       <c r="AB7" s="17" t="n"/>
       <c r="AC7" s="17" t="n"/>
-      <c r="AD7" s="16" t="n"/>
-      <c r="AE7" s="16" t="n"/>
+      <c r="AD7" s="32" t="n"/>
+      <c r="AE7" s="32" t="n"/>
       <c r="AF7" s="17" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="AG7" s="33">
+        <f>COUNTA(B7:AF7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Maja Dąbrowska</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="32" t="n"/>
+      <c r="J8" s="32" t="n"/>
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="M8" s="17" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="P8" s="16" t="n"/>
-      <c r="Q8" s="16" t="n"/>
-      <c r="R8" s="17" t="n"/>
-      <c r="S8" s="17" t="n"/>
-      <c r="T8" s="17" t="n"/>
-      <c r="U8" s="17" t="n"/>
-      <c r="V8" s="17" t="n"/>
-      <c r="W8" s="16" t="n"/>
-      <c r="X8" s="16" t="n"/>
-      <c r="Y8" s="17" t="n"/>
-      <c r="Z8" s="17" t="n"/>
-      <c r="AA8" s="17" t="n"/>
-      <c r="AB8" s="17" t="n"/>
-      <c r="AC8" s="17" t="n"/>
-      <c r="AD8" s="16" t="n"/>
-      <c r="AE8" s="16" t="n"/>
-      <c r="AF8" s="17" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
+      <c r="P8" s="32" t="n"/>
+      <c r="Q8" s="32" t="n"/>
+      <c r="R8" s="20" t="n"/>
+      <c r="S8" s="20" t="n"/>
+      <c r="T8" s="20" t="n"/>
+      <c r="U8" s="20" t="n"/>
+      <c r="V8" s="20" t="n"/>
+      <c r="W8" s="32" t="n"/>
+      <c r="X8" s="32" t="n"/>
+      <c r="Y8" s="20" t="n"/>
+      <c r="Z8" s="20" t="n"/>
+      <c r="AA8" s="20" t="n"/>
+      <c r="AB8" s="20" t="n"/>
+      <c r="AC8" s="20" t="n"/>
+      <c r="AD8" s="32" t="n"/>
+      <c r="AE8" s="32" t="n"/>
+      <c r="AF8" s="20" t="n"/>
+      <c r="AG8" s="33">
+        <f>COUNTA(B8:AF8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="31" t="n"/>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="32" t="n"/>
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
       <c r="F9" s="17" t="n"/>
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="17" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
+      <c r="I9" s="32" t="n"/>
+      <c r="J9" s="32" t="n"/>
       <c r="K9" s="17" t="n"/>
       <c r="L9" s="17" t="n"/>
       <c r="M9" s="17" t="n"/>
       <c r="N9" s="17" t="n"/>
       <c r="O9" s="17" t="n"/>
-      <c r="P9" s="16" t="n"/>
-      <c r="Q9" s="16" t="n"/>
+      <c r="P9" s="32" t="n"/>
+      <c r="Q9" s="32" t="n"/>
       <c r="R9" s="17" t="n"/>
       <c r="S9" s="17" t="n"/>
       <c r="T9" s="17" t="n"/>
       <c r="U9" s="17" t="n"/>
       <c r="V9" s="17" t="n"/>
-      <c r="W9" s="16" t="n"/>
-      <c r="X9" s="16" t="n"/>
+      <c r="W9" s="32" t="n"/>
+      <c r="X9" s="32" t="n"/>
       <c r="Y9" s="17" t="n"/>
       <c r="Z9" s="17" t="n"/>
       <c r="AA9" s="17" t="n"/>
       <c r="AB9" s="17" t="n"/>
       <c r="AC9" s="17" t="n"/>
-      <c r="AD9" s="16" t="n"/>
-      <c r="AE9" s="16" t="n"/>
+      <c r="AD9" s="32" t="n"/>
+      <c r="AE9" s="32" t="n"/>
       <c r="AF9" s="17" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="17" t="n"/>
-      <c r="L10" s="17" t="n"/>
-      <c r="M10" s="17" t="n"/>
-      <c r="N10" s="17" t="n"/>
-      <c r="O10" s="17" t="n"/>
-      <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="16" t="n"/>
-      <c r="R10" s="17" t="n"/>
-      <c r="S10" s="17" t="n"/>
-      <c r="T10" s="17" t="n"/>
-      <c r="U10" s="17" t="n"/>
-      <c r="V10" s="17" t="n"/>
-      <c r="W10" s="16" t="n"/>
-      <c r="X10" s="16" t="n"/>
-      <c r="Y10" s="17" t="n"/>
-      <c r="Z10" s="17" t="n"/>
-      <c r="AA10" s="17" t="n"/>
-      <c r="AB10" s="17" t="n"/>
-      <c r="AC10" s="17" t="n"/>
-      <c r="AD10" s="16" t="n"/>
-      <c r="AE10" s="16" t="n"/>
-      <c r="AF10" s="17" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
+      <c r="AG9" s="33">
+        <f>COUNTA(B9:AF9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="34" t="n"/>
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="32" t="n"/>
+      <c r="J10" s="32" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="L10" s="20" t="n"/>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="20" t="n"/>
+      <c r="P10" s="32" t="n"/>
+      <c r="Q10" s="32" t="n"/>
+      <c r="R10" s="20" t="n"/>
+      <c r="S10" s="20" t="n"/>
+      <c r="T10" s="20" t="n"/>
+      <c r="U10" s="20" t="n"/>
+      <c r="V10" s="20" t="n"/>
+      <c r="W10" s="32" t="n"/>
+      <c r="X10" s="32" t="n"/>
+      <c r="Y10" s="20" t="n"/>
+      <c r="Z10" s="20" t="n"/>
+      <c r="AA10" s="20" t="n"/>
+      <c r="AB10" s="20" t="n"/>
+      <c r="AC10" s="20" t="n"/>
+      <c r="AD10" s="32" t="n"/>
+      <c r="AE10" s="32" t="n"/>
+      <c r="AF10" s="20" t="n"/>
+      <c r="AG10" s="33">
+        <f>COUNTA(B10:AF10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="31" t="n"/>
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
       <c r="D11" s="17" t="n"/>
       <c r="E11" s="17" t="n"/>
       <c r="F11" s="17" t="n"/>
       <c r="G11" s="17" t="n"/>
       <c r="H11" s="17" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
+      <c r="I11" s="32" t="n"/>
+      <c r="J11" s="32" t="n"/>
       <c r="K11" s="17" t="n"/>
       <c r="L11" s="17" t="n"/>
       <c r="M11" s="17" t="n"/>
       <c r="N11" s="17" t="n"/>
       <c r="O11" s="17" t="n"/>
-      <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="16" t="n"/>
+      <c r="P11" s="32" t="n"/>
+      <c r="Q11" s="32" t="n"/>
       <c r="R11" s="17" t="n"/>
       <c r="S11" s="17" t="n"/>
       <c r="T11" s="17" t="n"/>
       <c r="U11" s="17" t="n"/>
       <c r="V11" s="17" t="n"/>
-      <c r="W11" s="16" t="n"/>
-      <c r="X11" s="16" t="n"/>
+      <c r="W11" s="32" t="n"/>
+      <c r="X11" s="32" t="n"/>
       <c r="Y11" s="17" t="n"/>
       <c r="Z11" s="17" t="n"/>
       <c r="AA11" s="17" t="n"/>
       <c r="AB11" s="17" t="n"/>
       <c r="AC11" s="17" t="n"/>
-      <c r="AD11" s="16" t="n"/>
-      <c r="AE11" s="16" t="n"/>
+      <c r="AD11" s="32" t="n"/>
+      <c r="AE11" s="32" t="n"/>
       <c r="AF11" s="17" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="17" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="17" t="n"/>
-      <c r="L12" s="17" t="n"/>
-      <c r="M12" s="17" t="n"/>
-      <c r="N12" s="17" t="n"/>
-      <c r="O12" s="17" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
-      <c r="R12" s="17" t="n"/>
-      <c r="S12" s="17" t="n"/>
-      <c r="T12" s="17" t="n"/>
-      <c r="U12" s="17" t="n"/>
-      <c r="V12" s="17" t="n"/>
-      <c r="W12" s="16" t="n"/>
-      <c r="X12" s="16" t="n"/>
-      <c r="Y12" s="17" t="n"/>
-      <c r="Z12" s="17" t="n"/>
-      <c r="AA12" s="17" t="n"/>
-      <c r="AB12" s="17" t="n"/>
-      <c r="AC12" s="17" t="n"/>
-      <c r="AD12" s="16" t="n"/>
-      <c r="AE12" s="16" t="n"/>
-      <c r="AF12" s="17" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
+      <c r="AG11" s="33">
+        <f>COUNTA(B11:AF11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="34" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="32" t="n"/>
+      <c r="J12" s="32" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="20" t="n"/>
+      <c r="O12" s="20" t="n"/>
+      <c r="P12" s="32" t="n"/>
+      <c r="Q12" s="32" t="n"/>
+      <c r="R12" s="20" t="n"/>
+      <c r="S12" s="20" t="n"/>
+      <c r="T12" s="20" t="n"/>
+      <c r="U12" s="20" t="n"/>
+      <c r="V12" s="20" t="n"/>
+      <c r="W12" s="32" t="n"/>
+      <c r="X12" s="32" t="n"/>
+      <c r="Y12" s="20" t="n"/>
+      <c r="Z12" s="20" t="n"/>
+      <c r="AA12" s="20" t="n"/>
+      <c r="AB12" s="20" t="n"/>
+      <c r="AC12" s="20" t="n"/>
+      <c r="AD12" s="32" t="n"/>
+      <c r="AE12" s="32" t="n"/>
+      <c r="AF12" s="20" t="n"/>
+      <c r="AG12" s="33">
+        <f>COUNTA(B12:AF12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="31" t="n"/>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="32" t="n"/>
       <c r="D13" s="17" t="n"/>
       <c r="E13" s="17" t="n"/>
       <c r="F13" s="17" t="n"/>
       <c r="G13" s="17" t="n"/>
       <c r="H13" s="17" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
+      <c r="I13" s="32" t="n"/>
+      <c r="J13" s="32" t="n"/>
       <c r="K13" s="17" t="n"/>
       <c r="L13" s="17" t="n"/>
       <c r="M13" s="17" t="n"/>
       <c r="N13" s="17" t="n"/>
       <c r="O13" s="17" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="16" t="n"/>
+      <c r="P13" s="32" t="n"/>
+      <c r="Q13" s="32" t="n"/>
       <c r="R13" s="17" t="n"/>
       <c r="S13" s="17" t="n"/>
       <c r="T13" s="17" t="n"/>
       <c r="U13" s="17" t="n"/>
       <c r="V13" s="17" t="n"/>
-      <c r="W13" s="16" t="n"/>
-      <c r="X13" s="16" t="n"/>
+      <c r="W13" s="32" t="n"/>
+      <c r="X13" s="32" t="n"/>
       <c r="Y13" s="17" t="n"/>
       <c r="Z13" s="17" t="n"/>
       <c r="AA13" s="17" t="n"/>
       <c r="AB13" s="17" t="n"/>
       <c r="AC13" s="17" t="n"/>
-      <c r="AD13" s="16" t="n"/>
-      <c r="AE13" s="16" t="n"/>
+      <c r="AD13" s="32" t="n"/>
+      <c r="AE13" s="32" t="n"/>
       <c r="AF13" s="17" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="17" t="n"/>
-      <c r="L14" s="17" t="n"/>
-      <c r="M14" s="17" t="n"/>
-      <c r="N14" s="17" t="n"/>
-      <c r="O14" s="17" t="n"/>
-      <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="16" t="n"/>
-      <c r="R14" s="17" t="n"/>
-      <c r="S14" s="17" t="n"/>
-      <c r="T14" s="17" t="n"/>
-      <c r="U14" s="17" t="n"/>
-      <c r="V14" s="17" t="n"/>
-      <c r="W14" s="16" t="n"/>
-      <c r="X14" s="16" t="n"/>
-      <c r="Y14" s="17" t="n"/>
-      <c r="Z14" s="17" t="n"/>
-      <c r="AA14" s="17" t="n"/>
-      <c r="AB14" s="17" t="n"/>
-      <c r="AC14" s="17" t="n"/>
-      <c r="AD14" s="16" t="n"/>
-      <c r="AE14" s="16" t="n"/>
-      <c r="AF14" s="17" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
+      <c r="AG13" s="33">
+        <f>COUNTA(B13:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="34" t="n"/>
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="32" t="n"/>
+      <c r="J14" s="32" t="n"/>
+      <c r="K14" s="20" t="n"/>
+      <c r="L14" s="20" t="n"/>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="20" t="n"/>
+      <c r="O14" s="20" t="n"/>
+      <c r="P14" s="32" t="n"/>
+      <c r="Q14" s="32" t="n"/>
+      <c r="R14" s="20" t="n"/>
+      <c r="S14" s="20" t="n"/>
+      <c r="T14" s="20" t="n"/>
+      <c r="U14" s="20" t="n"/>
+      <c r="V14" s="20" t="n"/>
+      <c r="W14" s="32" t="n"/>
+      <c r="X14" s="32" t="n"/>
+      <c r="Y14" s="20" t="n"/>
+      <c r="Z14" s="20" t="n"/>
+      <c r="AA14" s="20" t="n"/>
+      <c r="AB14" s="20" t="n"/>
+      <c r="AC14" s="20" t="n"/>
+      <c r="AD14" s="32" t="n"/>
+      <c r="AE14" s="32" t="n"/>
+      <c r="AF14" s="20" t="n"/>
+      <c r="AG14" s="33">
+        <f>COUNTA(B14:AF14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="31" t="n"/>
+      <c r="B15" s="32" t="n"/>
+      <c r="C15" s="32" t="n"/>
       <c r="D15" s="17" t="n"/>
       <c r="E15" s="17" t="n"/>
       <c r="F15" s="17" t="n"/>
       <c r="G15" s="17" t="n"/>
       <c r="H15" s="17" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="16" t="n"/>
+      <c r="I15" s="32" t="n"/>
+      <c r="J15" s="32" t="n"/>
       <c r="K15" s="17" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="17" t="n"/>
       <c r="N15" s="17" t="n"/>
       <c r="O15" s="17" t="n"/>
-      <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="16" t="n"/>
+      <c r="P15" s="32" t="n"/>
+      <c r="Q15" s="32" t="n"/>
       <c r="R15" s="17" t="n"/>
       <c r="S15" s="17" t="n"/>
       <c r="T15" s="17" t="n"/>
       <c r="U15" s="17" t="n"/>
       <c r="V15" s="17" t="n"/>
-      <c r="W15" s="16" t="n"/>
-      <c r="X15" s="16" t="n"/>
+      <c r="W15" s="32" t="n"/>
+      <c r="X15" s="32" t="n"/>
       <c r="Y15" s="17" t="n"/>
       <c r="Z15" s="17" t="n"/>
       <c r="AA15" s="17" t="n"/>
       <c r="AB15" s="17" t="n"/>
       <c r="AC15" s="17" t="n"/>
-      <c r="AD15" s="16" t="n"/>
-      <c r="AE15" s="16" t="n"/>
+      <c r="AD15" s="32" t="n"/>
+      <c r="AE15" s="32" t="n"/>
       <c r="AF15" s="17" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="17" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="16" t="n"/>
-      <c r="K16" s="17" t="n"/>
-      <c r="L16" s="17" t="n"/>
-      <c r="M16" s="17" t="n"/>
-      <c r="N16" s="17" t="n"/>
-      <c r="O16" s="17" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-      <c r="R16" s="17" t="n"/>
-      <c r="S16" s="17" t="n"/>
-      <c r="T16" s="17" t="n"/>
-      <c r="U16" s="17" t="n"/>
-      <c r="V16" s="17" t="n"/>
-      <c r="W16" s="16" t="n"/>
-      <c r="X16" s="16" t="n"/>
-      <c r="Y16" s="17" t="n"/>
-      <c r="Z16" s="17" t="n"/>
-      <c r="AA16" s="17" t="n"/>
-      <c r="AB16" s="17" t="n"/>
-      <c r="AC16" s="17" t="n"/>
-      <c r="AD16" s="16" t="n"/>
-      <c r="AE16" s="16" t="n"/>
-      <c r="AF16" s="17" t="n"/>
+      <c r="AG15" s="33">
+        <f>COUNTA(B15:AF15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="34" t="n"/>
+      <c r="B16" s="32" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="32" t="n"/>
+      <c r="J16" s="32" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="20" t="n"/>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="20" t="n"/>
+      <c r="O16" s="20" t="n"/>
+      <c r="P16" s="32" t="n"/>
+      <c r="Q16" s="32" t="n"/>
+      <c r="R16" s="20" t="n"/>
+      <c r="S16" s="20" t="n"/>
+      <c r="T16" s="20" t="n"/>
+      <c r="U16" s="20" t="n"/>
+      <c r="V16" s="20" t="n"/>
+      <c r="W16" s="32" t="n"/>
+      <c r="X16" s="32" t="n"/>
+      <c r="Y16" s="20" t="n"/>
+      <c r="Z16" s="20" t="n"/>
+      <c r="AA16" s="20" t="n"/>
+      <c r="AB16" s="20" t="n"/>
+      <c r="AC16" s="20" t="n"/>
+      <c r="AD16" s="32" t="n"/>
+      <c r="AE16" s="32" t="n"/>
+      <c r="AF16" s="20" t="n"/>
+      <c r="AG16" s="33">
+        <f>COUNTA(B16:AF16)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D1:T1"/>
+  </mergeCells>
   <conditionalFormatting sqref="B5:AF16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"X"</formula>
@@ -1917,12 +2201,13 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="A5:A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Imię i nazwisko" prompt="Wybierz siebie z listy z zakładki Pracownicy." type="list">
-      <formula1>=Pracownicy!$A$2:$A$13</formula1>
+      <formula1>=Pracownicy!$A$4:$A$15</formula1>
     </dataValidation>
-    <dataValidation sqref="B5:AF16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Kod dostępności" error="Dozwolone kody: X (cały dzień), D (rano / dzień), N (noc). Puste pole = jestem dostępny." promptTitle="Niedostępność" prompt="X = cały dzień, D = rano / dzień, N = noc. Puste = dostępny." type="list">
+    <dataValidation sqref="B5:AF16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Kod dostępności" error="Dozwolone kody: X (cały dzień), D (rano / dzień), N (noc). Puste pole = jestem dostępny." promptTitle="Niedostępność" prompt="X = cały dzień, D = rano / dzień, N = noc." type="list">
       <formula1>"X,D,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/templates/Grafik-dane-2026-08-przyklad.xlsx
+++ b/templates/Grafik-dane-2026-08-przyklad.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Instrukcja" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Pracownicy" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Dostępność" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Administrator" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,24 +453,39 @@
         <t>Czy bierzesz dyżury 24-godzinne i w jakim układzie.</t>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0">
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Grafik</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
       <text>
-        <t>Twoje kwalifikacje, po przecinku. Domyślnie: General.</t>
+        <t>Musi brzmieć tak samo jak w zakładce Pracownicy.</t>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0">
+    <comment ref="B3" authorId="0" shapeId="0">
       <text>
-        <t>Tak, jeśli możesz pełnić zmianę kierownika.</t>
+        <t>Kwalifikacje, po przecinku. Puste = General.</t>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Tak, jeśli ta osoba może pełnić zmianę kierownika.</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Tak tylko dla jednej osoby w zespole.</t>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0">
+    <comment ref="E3" authorId="0" shapeId="0">
       <text>
-        <t>Pole dowolne — program je pomija.</t>
+        <t>Notatki osoby układającej grafik — program je pomija.</t>
       </text>
     </comment>
   </commentList>
@@ -766,7 +782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -841,67 +857,67 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Zakładka „Administrator”</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Należy do osoby układającej grafik: kwalifikacje, uprawnienia kierownika i notatki. Arkusz jest chroniony — pracownicy go nie zmieniają.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="8" customHeight="1">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Kody dostępności</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>niedostępny przez cały dzień (urlop, L4)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>niedostępny rano i w dzień — noce są w porządku</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>niedostępny w nocy — dni są w porządku</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>puste pole — jestem dostępny</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="8" customHeight="1">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>O czym pamiętać</t>
         </is>
       </c>
     </row>
@@ -909,49 +925,69 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
+          <t>puste pole — jestem dostępny</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="8" customHeight="1">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>O czym pamiętać</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>Imię i nazwisko musi brzmieć tak samo w obu zakładkach — w „Dostępności” wybierz je z listy.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Nie zmieniaj nazw zakładek ani nagłówków kolumn — po nich program rozpoznaje dane.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Możesz dopisywać wiersze na dole i dodawać własne kolumny; program pomija to, czego nie zna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="8" customHeight="1">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Dla osoby układającej grafik</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
+          <t>Możesz dopisywać wiersze na dole i dodawać własne kolumny; program pomija to, czego nie zna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="8" customHeight="1">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Dla osoby układającej grafik</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>Gdy zespół skończy: Plik → Pobierz → Microsoft Excel (.xlsx), a następnie w programie Shiftwise zakładka Workers → Import from sheet. Przed zapisem zobaczysz podgląd wszystkich zmian.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" s="11" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Miesiąc, którego dotyczy arkusz, jest w komórce B1 zakładki „Dostępność”. Aby użyć tego samego arkusza w kolejnym miesiącu, zmień tę komórkę i wyczyść siatkę.</t>
         </is>
@@ -969,17 +1005,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -992,7 +1024,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>Jeden wiersz na osobę · sierpień 2026</t>
+          <t>Jeden wiersz na osobę · sierpień 2026 · wypełniają pracownicy</t>
         </is>
       </c>
     </row>
@@ -1017,26 +1049,6 @@
           <t>Dyżur 24h</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>Kategorie</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>Uprawnienia kierownika</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>Kierownik domyślny</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t>Uwagi</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
@@ -1057,22 +1069,6 @@
           <t>Nie</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>Tak</t>
-        </is>
-      </c>
-      <c r="G4" s="17" t="inlineStr">
-        <is>
-          <t>Tak</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
@@ -1093,26 +1089,6 @@
           <t>Dowolny</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>Wolę bloki nocne.</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
@@ -1133,22 +1109,6 @@
           <t>08:00 → 08:00</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>Tak</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
@@ -1167,26 +1127,6 @@
       <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Nie</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>Urlop w drugim tygodniu.</t>
         </is>
       </c>
     </row>
@@ -1195,94 +1135,56 @@
       <c r="B8" s="16" t="n"/>
       <c r="C8" s="17" t="n"/>
       <c r="D8" s="17" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="15" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="18" t="n"/>
       <c r="B9" s="19" t="n"/>
       <c r="C9" s="20" t="n"/>
       <c r="D9" s="20" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="18" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="n"/>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="17" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="15" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="18" t="n"/>
       <c r="B11" s="19" t="n"/>
       <c r="C11" s="20" t="n"/>
       <c r="D11" s="20" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="18" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="15" t="n"/>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="17" t="n"/>
       <c r="D12" s="17" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="15" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="18" t="n"/>
       <c r="B13" s="19" t="n"/>
       <c r="C13" s="20" t="n"/>
       <c r="D13" s="20" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="18" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="n"/>
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="17" t="n"/>
       <c r="D14" s="17" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="15" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="18" t="n"/>
       <c r="B15" s="19" t="n"/>
       <c r="C15" s="20" t="n"/>
       <c r="D15" s="20" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="18" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="3">
     <dataValidation sqref="C4:C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Preferowana pora" error="Wybierz: Dzień, Noc albo Bez preferencji." promptTitle="Preferowana pora" prompt="Wybierz: Dzień, Noc albo Bez preferencji." type="list">
       <formula1>"Dzień,Noc,Bez preferencji"</formula1>
     </dataValidation>
     <dataValidation sqref="D4:D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Dyżur 24h" error="Nie, Dowolny albo konkretny układ 24-godzinny." promptTitle="Dyżur 24h" prompt="Nie, Dowolny albo konkretny układ 24-godzinny." type="list">
       <formula1>"Nie,Dowolny,08:00 → 08:00,20:00 → 20:00"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Uprawnienia kierownika" error="Tak albo Nie." promptTitle="Uprawnienia kierownika" prompt="Tak albo Nie." type="list">
-      <formula1>"Tak,Nie"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Kierownik domyślny" error="Tak tylko dla jednej osoby w zespole." promptTitle="Kierownik domyślny" prompt="Tak tylko dla jednej osoby w zespole." type="list">
-      <formula1>"Tak,Nie"</formula1>
     </dataValidation>
     <dataValidation sqref="B4:B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Godziny docelowe" error="Podaj liczbę godzin z zakresu 0–400." promptTitle="Godziny docelowe" prompt="Ile godzin chcesz przepracować w tym miesiącu." type="whole" operator="between">
       <formula1>0</formula1>
@@ -2210,4 +2112,236 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="006B7A72"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Kwalifikacje i role kierownika · sierpień 2026 · wypełnia osoba układająca grafik</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Imię i nazwisko</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Kategorie</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Uprawnienia kierownika</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Kierownik domyślny</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Łukasz Zieliński</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Agnieszka Wójcik</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Nie</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Nie</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>Wolę bloki nocne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Paweł Nowak</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>General, Nursing</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Nie</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Maja Dąbrowska</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Nie</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Nie</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Urlop w drugim tygodniu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="18" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="18" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <dataValidations count="3">
+    <dataValidation sqref="C4:C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Tak albo Nie" error="Wpisz Tak albo Nie." type="list">
+      <formula1>"Tak,Nie"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D4:D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Tak albo Nie" error="Wpisz Tak albo Nie." type="list">
+      <formula1>"Tak,Nie"</formula1>
+    </dataValidation>
+    <dataValidation sqref="A4:A15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Imię i nazwisko" prompt="Wybierz osobę z zakładki Pracownicy." type="list">
+      <formula1>=Pracownicy!$A$4:$A$15</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>